--- a/data/inventario.xlsx
+++ b/data/inventario.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5dde90e77e994304/Escritorio/Sistema de Compras en Línea/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5dde90e77e994304/Escritorio/Tienda en Línea 2.0/tienda-catalogo/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="315" documentId="11_2843655783A97BB1E0958767EB3491E1E1F26E46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D7166F7-AA9C-4497-B8E5-EC99874B1934}"/>
+  <xr:revisionPtr revIDLastSave="419" documentId="11_2843655783A97BB1E0958767EB3491E1E1F26E46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76F0D447-B083-4596-8542-4AD783DEA9F0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="149">
   <si>
     <t>ID</t>
   </si>
@@ -140,12 +140,6 @@
     <t>925154.jpg</t>
   </si>
   <si>
-    <t>Aretes sin baño diseño moderno perla tono blanco pulido</t>
-  </si>
-  <si>
-    <t>Aretes sin baño que destacan por su perla en tono blanco con acabado pulido y forma moderna. Su diseño orgánico aporta un aire distinguido y actual, convirtiéndolos en el accesorio perfecto para realzar desde atuendos casuales hasta looks más sofisticados y llenos de originalidad.</t>
-  </si>
-  <si>
     <t>925434L.jpg</t>
   </si>
   <si>
@@ -161,9 +155,6 @@
     <t>Aretes</t>
   </si>
   <si>
-    <t>Collar</t>
-  </si>
-  <si>
     <t>124701.jpg</t>
   </si>
   <si>
@@ -176,9 +167,6 @@
     <t>Collar infantil en baño de oro con dijes de estrellas esmaltadas</t>
   </si>
   <si>
-    <t>Collar infantil de corazones</t>
-  </si>
-  <si>
     <t>Labial</t>
   </si>
   <si>
@@ -263,9 +251,6 @@
     <t>sun.jpg</t>
   </si>
   <si>
-    <t>Dr. C. Tuna Aqua Gotas Impulsantes de Hidratación</t>
-  </si>
-  <si>
     <t>Un suero facial ligero y de absorción rápida que ayuda a lograr una hidratación profunda y a proteger la piel de la contaminación. Tez visiblemente más radiante y de aspecto saludable. Ideal para pieles deshidratadas. Probado dermatológicamente.</t>
   </si>
   <si>
@@ -291,9 +276,6 @@
   </si>
   <si>
     <t>jabones.jpg</t>
-  </si>
-  <si>
-    <t>Jabones en barra naturé</t>
   </si>
   <si>
     <t>Crema hidratante corporal mango rosa y agua de coco</t>
@@ -403,9 +385,6 @@
     <t>jabonesmango.jpg</t>
   </si>
   <si>
-    <t>Desodorante antimanchas roll on Tododia - 70 ml - Tododia</t>
-  </si>
-  <si>
     <t>Desodorante</t>
   </si>
   <si>
@@ -413,6 +392,96 @@
   </si>
   <si>
     <t>deso.jpg</t>
+  </si>
+  <si>
+    <t>deso2.jpg</t>
+  </si>
+  <si>
+    <t>Protege, hidrata y acoge todos los tonos de piel</t>
+  </si>
+  <si>
+    <t>Pulpa hidratante para manos castaña - 75 g - Ekos</t>
+  </si>
+  <si>
+    <t>48 horas de hidratación para las manos y uñas con el poder antirresequedad de la castaña.</t>
+  </si>
+  <si>
+    <t>pulpa.jpg</t>
+  </si>
+  <si>
+    <t>Trazo preciso, mirada marcante</t>
+  </si>
+  <si>
+    <t>Delineador</t>
+  </si>
+  <si>
+    <t>deli.jpg</t>
+  </si>
+  <si>
+    <t>Válvula - 1 unidad - Aguas Natura</t>
+  </si>
+  <si>
+    <t>Adquiere la válvula por separado</t>
+  </si>
+  <si>
+    <t>Válvula</t>
+  </si>
+  <si>
+    <t>valv.jpg</t>
+  </si>
+  <si>
+    <t>Aretes largos de bolitas</t>
+  </si>
+  <si>
+    <t>Aretes forma de gota sin baño diseño moderno perla tono blanco pulido</t>
+  </si>
+  <si>
+    <t>Aretes forma de gota sin baño que destacan por su perla en tono blanco con acabado pulido y forma moderna. Su diseño orgánico aporta un aire distinguido y actual, convirtiéndolos en el accesorio perfecto para realzar desde atuendos casuales hasta looks más sofisticados y llenos de originalidad.</t>
+  </si>
+  <si>
+    <t>Collar infantil de corazones y mariposas</t>
+  </si>
+  <si>
+    <t>Dr. C. Tuna Aqua Gotas Impulsantes de Hidratación suero facial</t>
+  </si>
+  <si>
+    <t>Jabones en barra naturé infantil</t>
+  </si>
+  <si>
+    <t>Desodorante fragancia de algodoón antimanchas roll on Tododia - 70 ml - Tododia</t>
+  </si>
+  <si>
+    <t>Desodorante antimanchas piel uniforme roll on Tododia - 70 ml - Tododia</t>
+  </si>
+  <si>
+    <t>Delineador negro en fibra para ojos - 1 ml - Faces</t>
+  </si>
+  <si>
+    <t>Aretes largos en baño de oro con luna y estrella</t>
+  </si>
+  <si>
+    <t>luna.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collar de colibrí </t>
+  </si>
+  <si>
+    <t>colibri.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aretes de colibrí en pleno vuelo </t>
+  </si>
+  <si>
+    <t>colibrivuelvo.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cadena Con Dije Triple Cuadrado En Platino </t>
+  </si>
+  <si>
+    <t>Cadena</t>
+  </si>
+  <si>
+    <t>cadena.jpg</t>
   </si>
 </sst>
 </file>
@@ -422,7 +491,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\$#,##0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -447,6 +516,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -485,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -501,13 +576,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -810,13 +894,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
+    <col min="3" max="3" width="59.33203125" customWidth="1"/>
+    <col min="4" max="4" width="67.33203125" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
@@ -871,13 +955,13 @@
         <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4">
@@ -913,7 +997,7 @@
         <v>33</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4">
@@ -949,7 +1033,7 @@
         <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
@@ -978,14 +1062,14 @@
       <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>40</v>
+      <c r="C5" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
@@ -1015,13 +1099,13 @@
         <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="F6" s="4">
         <v>499</v>
@@ -1033,7 +1117,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>13</v>
@@ -1053,13 +1137,13 @@
         <v>12</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4">
@@ -1069,7 +1153,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>14</v>
@@ -1089,13 +1173,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>51</v>
+        <v>134</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4">
@@ -1105,7 +1189,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>13</v>
@@ -1125,13 +1209,13 @@
         <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4">
@@ -1141,7 +1225,7 @@
         <v>3</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>13</v>
@@ -1161,13 +1245,13 @@
         <v>15</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4">
@@ -1177,7 +1261,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>13</v>
@@ -1197,10 +1281,10 @@
         <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>16</v>
@@ -1213,7 +1297,7 @@
         <v>2</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>14</v>
@@ -1233,13 +1317,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F12" s="4">
         <v>110</v>
@@ -1251,7 +1335,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>13</v>
@@ -1271,13 +1355,13 @@
         <v>15</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F13" s="4">
         <v>110</v>
@@ -1289,7 +1373,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>13</v>
@@ -1309,13 +1393,13 @@
         <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F14" s="4">
         <v>110</v>
@@ -1327,7 +1411,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>13</v>
@@ -1347,13 +1431,13 @@
         <v>15</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4">
@@ -1363,7 +1447,7 @@
         <v>2</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>13</v>
@@ -1383,13 +1467,13 @@
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4">
@@ -1399,7 +1483,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>13</v>
@@ -1418,14 +1502,14 @@
       <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>80</v>
+      <c r="C17" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F17" s="4">
         <v>900</v>
@@ -1437,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1457,13 +1541,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4">
@@ -1473,7 +1557,7 @@
         <v>1</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>13</v>
@@ -1492,14 +1576,14 @@
       <c r="B19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>90</v>
+      <c r="C19" s="7" t="s">
+        <v>136</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4">
@@ -1509,7 +1593,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1529,13 +1613,13 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4">
@@ -1545,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>14</v>
@@ -1565,13 +1649,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4">
@@ -1581,7 +1665,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1601,13 +1685,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F22" s="4">
         <v>370</v>
@@ -1619,307 +1703,737 @@
         <v>1</v>
       </c>
       <c r="I22" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>18</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="10">
+        <v>699</v>
+      </c>
+      <c r="G23" s="10">
+        <v>459</v>
+      </c>
+      <c r="H23" s="8">
+        <v>1</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>19</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10">
+        <v>99</v>
+      </c>
+      <c r="H24" s="8">
+        <v>1</v>
+      </c>
+      <c r="I24" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="J22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
+      <c r="J24" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>20</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C25" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10">
+        <v>210</v>
+      </c>
+      <c r="H25" s="8">
+        <v>1</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>21</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F23" s="4">
-        <v>699</v>
-      </c>
-      <c r="G23" s="4">
-        <v>459</v>
-      </c>
-      <c r="H23" s="2">
-        <v>1</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>19</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="C26" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10">
+        <v>559</v>
+      </c>
+      <c r="H26" s="8">
+        <v>1</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="11">
+        <v>22</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4">
-        <v>99</v>
-      </c>
-      <c r="H24" s="2">
-        <v>1</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <v>20</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="C27" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="10">
+        <v>409</v>
+      </c>
+      <c r="G27" s="13">
+        <v>379</v>
+      </c>
+      <c r="H27" s="11">
+        <v>1</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="14">
+        <v>23</v>
+      </c>
+      <c r="B28" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4">
-        <v>210</v>
-      </c>
-      <c r="H25" s="2">
-        <v>1</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>21</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="C28" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10">
+        <v>460</v>
+      </c>
+      <c r="H28" s="8">
+        <v>1</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="14">
+        <v>24</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4">
-        <v>559</v>
-      </c>
-      <c r="H26" s="2">
-        <v>1</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="9">
-        <v>22</v>
-      </c>
-      <c r="B27" s="10" t="s">
+      <c r="C29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F29" s="12"/>
+      <c r="G29" s="13">
+        <v>230</v>
+      </c>
+      <c r="H29" s="8">
+        <v>1</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="14">
+        <v>25</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D27" t="s">
-        <v>111</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="F27" s="4">
-        <v>409</v>
-      </c>
-      <c r="G27" s="12">
-        <v>379</v>
-      </c>
-      <c r="H27" s="9">
-        <v>1</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="9">
-        <v>23</v>
-      </c>
-      <c r="B28" s="10" t="s">
+      <c r="C30" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F30" s="12"/>
+      <c r="G30" s="13">
+        <v>143</v>
+      </c>
+      <c r="H30" s="11">
+        <v>1</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>26</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" s="10" t="s">
+      <c r="C31" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E31" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="E28" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4">
-        <v>460</v>
-      </c>
-      <c r="H28" s="9">
-        <v>1</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="9">
-        <v>24</v>
-      </c>
-      <c r="B29" s="10" t="s">
+      <c r="F31" s="12"/>
+      <c r="G31" s="13">
+        <v>143</v>
+      </c>
+      <c r="H31" s="8">
+        <v>1</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>27</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="G29" s="12">
-        <v>230</v>
-      </c>
-      <c r="H29" s="9">
-        <v>1</v>
-      </c>
-      <c r="I29" s="13" t="s">
+      <c r="C32" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="J29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="9">
-        <v>25</v>
-      </c>
-      <c r="B30" s="10" t="s">
+      <c r="D32" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32" s="12"/>
+      <c r="G32" s="13">
+        <v>209</v>
+      </c>
+      <c r="H32" s="8">
+        <v>1</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="11">
+        <v>28</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C30" t="s">
-        <v>122</v>
-      </c>
-      <c r="D30" s="10" t="s">
+      <c r="C33" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="E30" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="G30" s="12">
+      <c r="E33" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="G33" s="13">
+        <v>200</v>
+      </c>
+      <c r="H33" s="8">
+        <v>1</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="14">
+        <v>29</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="F34" s="12"/>
+      <c r="G34" s="13">
+        <v>79</v>
+      </c>
+      <c r="H34" s="8">
+        <v>1</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="14">
+        <v>30</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" s="12"/>
+      <c r="G35" s="13">
+        <v>319</v>
+      </c>
+      <c r="H35" s="16">
+        <v>1</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="14">
+        <v>31</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F36" s="12"/>
+      <c r="G36" s="13">
+        <v>399</v>
+      </c>
+      <c r="H36" s="16">
+        <v>1</v>
+      </c>
+      <c r="I36" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="H30" s="9">
-        <v>1</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="J36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="15">
+        <v>32</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="12"/>
+      <c r="G37" s="13">
+        <v>179</v>
+      </c>
+      <c r="H37" s="16">
+        <v>1</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="15">
+        <v>34</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="F38" s="12"/>
+      <c r="G38" s="13">
+        <v>469</v>
+      </c>
+      <c r="H38" s="16">
+        <v>1</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="15"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="12"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="15"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="12"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="15"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
+      <c r="L41" s="12"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="12"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="12"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="12"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="12"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="12"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="12"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="12"/>
+      <c r="L45" s="12"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="12"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="12"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="12"/>
+      <c r="L47" s="12"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="12"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
